--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4977,6 +4977,263 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122513015</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57532</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mosstorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>670529</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6615739</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ett par vid lämplig boplats.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122513010</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57395</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mosstorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>670529</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6615739</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Caroline Kling</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -4979,7 +4979,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122513015</v>
+        <v>122513016</v>
       </c>
       <c r="B40" t="n">
         <v>57532</v>
@@ -4997,11 +4997,6 @@
       <c r="E40" t="n">
         <v>103021</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -5014,13 +5009,13 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5070,7 +5065,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,12 +5075,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ett par vid lämplig boplats.</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5129,11 +5119,6 @@
       </c>
       <c r="E41" t="n">
         <v>100049</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -4979,10 +4979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122513016</v>
+        <v>122513015</v>
       </c>
       <c r="B40" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4997,6 +4997,11 @@
       <c r="E40" t="n">
         <v>103021</v>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -5009,13 +5014,13 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5065,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5075,7 +5080,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ett par vid lämplig boplats.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5105,7 +5115,7 @@
         <v>122513010</v>
       </c>
       <c r="B41" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5119,6 +5129,11 @@
       </c>
       <c r="E41" t="n">
         <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -4979,7 +4979,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122513015</v>
+        <v>122513016</v>
       </c>
       <c r="B40" t="n">
         <v>57536</v>
@@ -5014,13 +5014,13 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,12 +5080,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ett par vid lämplig boplats.</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -4979,7 +4979,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122513016</v>
+        <v>122513015</v>
       </c>
       <c r="B40" t="n">
         <v>57536</v>
@@ -5014,13 +5014,13 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,7 +5080,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ett par vid lämplig boplats.</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -4982,7 +4982,7 @@
         <v>122513016</v>
       </c>
       <c r="B40" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>122513010</v>
       </c>
       <c r="B41" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -4979,10 +4979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122513016</v>
+        <v>122513010</v>
       </c>
       <c r="B40" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4995,21 +4995,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5018,11 +5018,7 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -5070,7 +5066,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,7 +5076,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5107,10 +5103,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122513010</v>
+        <v>122513016</v>
       </c>
       <c r="B41" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5123,21 +5119,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5146,7 +5142,11 @@
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -4979,10 +4979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122513010</v>
+        <v>122513016</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4995,21 +4995,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5018,7 +5018,11 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -5066,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5076,7 +5080,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5103,10 +5107,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122513015</v>
+        <v>122513010</v>
       </c>
       <c r="B41" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5119,34 +5123,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5204,12 +5204,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ett par vid lämplig boplats.</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -4979,10 +4979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122513016</v>
+        <v>122513010</v>
       </c>
       <c r="B40" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4995,21 +4995,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5018,11 +5018,7 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -5070,7 +5066,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,7 +5076,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5107,10 +5103,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122513010</v>
+        <v>122513016</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5123,21 +5119,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5146,7 +5142,11 @@
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 20030-2020 artfynd.xlsx
+++ b/artfynd/A 20030-2020 artfynd.xlsx
@@ -5103,7 +5103,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122513016</v>
+        <v>122513015</v>
       </c>
       <c r="B41" t="n">
         <v>57631</v>
@@ -5138,13 +5138,13 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5204,7 +5204,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ett par vid lämplig boplats.</t>
         </is>
       </c>
       <c r="AD41" t="b">
